--- a/modelos/mapa_temperatura/modelo_mapa_temperatura_controlados.xlsx
+++ b/modelos/mapa_temperatura/modelo_mapa_temperatura_controlados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Qualidade\04 - GED\02_Procedimentos e Controles\03_Filiais\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8E4776CA-5A4A-4C9F-8EC8-F8C05A9B67CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1521A669-7DF6-4986-A9FB-4A36CA869654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-915" windowWidth="29040" windowHeight="15720" xr2:uid="{D092D4B2-4342-4F8D-9AE4-44E0455EE4A5}"/>
   </bookViews>
@@ -218,32 +218,13 @@
     <t>7.</t>
   </si>
   <si>
-    <r>
-      <t>Ao receber o certificado de calibração do termômetro, o farmacêutico deve verificar se há algum desvio  fora da faixa esperada (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>± 1,0°C para temperatura e ± 5,0% para umidade) . O certificado deve ser assinado no verso indicando se o laudo está Aprovado ou Reprovado, conforme tópico 5 do QUA-POP-000212 Calibração de Termômetro e Termo-higrômetro</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
+    <t xml:space="preserve"> Ao receber o certificado de calibração do termômetro, o farmacêutico deve verificar se há algum desvio  fora da faixa esperada  (± 1,0°C para temperatura e ± 5,0% para umidade) .  O certificado deve ser   assinado no verso indicando se o laudo está Aprovado ou Reprovado, conforme tópico 5 do QUA-POP-000212 Calibração de Termômetro e Termo-higrômetro.</t>
   </si>
   <si>
     <t>8.</t>
   </si>
   <si>
-    <t>Toda vez que houver excursão de temperatura ou umidade, seja nos registros de mínima, máxima ou de momento, deve ser registrado o motivo no campo Medida corretiva/Justificativa,.</t>
+    <t>Toda vez que houver excursão de temperatura ou umidade, seja nos registros de mínima, máxima ou de momento, deve ser registrado o motivo no campo Medida corretiva/Justificativa.</t>
   </si>
   <si>
     <t>9.</t>
@@ -349,7 +330,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -396,11 +377,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <i/>
       <sz val="11"/>
@@ -436,15 +412,15 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="1"/>
+      <sz val="10.5"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="10.5"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
@@ -881,175 +857,173 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1072,9 +1046,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>47626</xdr:colOff>
+      <xdr:colOff>1</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>88611</xdr:rowOff>
+      <xdr:rowOff>12411</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2355554" cy="759114"/>
     <xdr:pic>
@@ -1104,7 +1078,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="47626" y="307686"/>
+          <a:off x="1" y="231486"/>
           <a:ext cx="2355554" cy="759114"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1417,259 +1391,258 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U58"/>
+  <dimension ref="A1:V58"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.140625" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="5" width="7.42578125" customWidth="1"/>
     <col min="6" max="6" width="6.5703125" customWidth="1"/>
-    <col min="7" max="7" width="12.28515625" customWidth="1"/>
-    <col min="8" max="8" width="8.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9" customWidth="1"/>
     <col min="9" max="11" width="7.42578125" customWidth="1"/>
     <col min="12" max="12" width="6.85546875" customWidth="1"/>
-    <col min="13" max="13" width="12.28515625" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="13" max="14" width="9" customWidth="1"/>
     <col min="15" max="17" width="7.42578125" customWidth="1"/>
     <col min="18" max="18" width="6.85546875" customWidth="1"/>
-    <col min="19" max="19" width="12.28515625" customWidth="1"/>
-    <col min="20" max="20" width="11.28515625" style="22" customWidth="1"/>
-    <col min="21" max="21" width="18.140625" style="22" customWidth="1"/>
+    <col min="19" max="19" width="9" customWidth="1"/>
+    <col min="20" max="20" width="22" style="19" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="18.140625" style="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="17.45" customHeight="1">
-      <c r="A1" s="36"/>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="38" t="s">
+    <row r="1" spans="1:22" ht="17.45" customHeight="1">
+      <c r="A1" s="43"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="38"/>
-      <c r="N1" s="38"/>
-      <c r="O1" s="38"/>
-      <c r="P1" s="38"/>
-      <c r="Q1" s="38"/>
-      <c r="R1" s="38"/>
-      <c r="S1" s="38"/>
-      <c r="T1" s="54" t="s">
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="59"/>
+      <c r="M1" s="59"/>
+      <c r="N1" s="59"/>
+      <c r="O1" s="59"/>
+      <c r="P1" s="59"/>
+      <c r="Q1" s="59"/>
+      <c r="R1" s="59"/>
+      <c r="S1" s="59"/>
+      <c r="T1" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="U1" s="23">
+      <c r="U1" s="63">
         <v>46507</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="15" customHeight="1">
-      <c r="A2" s="36"/>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="39" t="s">
+    <row r="2" spans="1:22">
+      <c r="A2" s="43"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
-      <c r="M2" s="39"/>
-      <c r="N2" s="39"/>
-      <c r="O2" s="39"/>
-      <c r="P2" s="39"/>
-      <c r="Q2" s="39"/>
-      <c r="R2" s="39"/>
-      <c r="S2" s="39"/>
-      <c r="T2" s="55"/>
-      <c r="U2" s="24"/>
-    </row>
-    <row r="3" spans="1:21" ht="15" customHeight="1">
-      <c r="A3" s="36"/>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="39"/>
-      <c r="L3" s="39"/>
-      <c r="M3" s="39"/>
-      <c r="N3" s="39"/>
-      <c r="O3" s="39"/>
-      <c r="P3" s="39"/>
-      <c r="Q3" s="39"/>
-      <c r="R3" s="39"/>
-      <c r="S3" s="39"/>
-      <c r="T3" s="56"/>
-      <c r="U3" s="25"/>
-    </row>
-    <row r="4" spans="1:21" ht="15.95" customHeight="1">
-      <c r="A4" s="36"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="40" t="s">
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
+      <c r="K2" s="75"/>
+      <c r="L2" s="75"/>
+      <c r="M2" s="75"/>
+      <c r="N2" s="75"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="75"/>
+      <c r="Q2" s="75"/>
+      <c r="R2" s="75"/>
+      <c r="S2" s="75"/>
+      <c r="T2" s="54"/>
+      <c r="U2" s="64"/>
+    </row>
+    <row r="3" spans="1:22">
+      <c r="A3" s="43"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
+      <c r="K3" s="75"/>
+      <c r="L3" s="75"/>
+      <c r="M3" s="75"/>
+      <c r="N3" s="75"/>
+      <c r="O3" s="75"/>
+      <c r="P3" s="75"/>
+      <c r="Q3" s="75"/>
+      <c r="R3" s="75"/>
+      <c r="S3" s="75"/>
+      <c r="T3" s="55"/>
+      <c r="U3" s="65"/>
+    </row>
+    <row r="4" spans="1:22" ht="15.95" customHeight="1">
+      <c r="A4" s="43"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="41"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="37" t="s">
+      <c r="G4" s="61"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="J4" s="37"/>
-      <c r="K4" s="37"/>
-      <c r="L4" s="37"/>
-      <c r="M4" s="37"/>
-      <c r="N4" s="37"/>
-      <c r="O4" s="37"/>
-      <c r="P4" s="37"/>
-      <c r="Q4" s="37"/>
-      <c r="R4" s="37"/>
-      <c r="S4" s="37"/>
-      <c r="T4" s="26" t="s">
+      <c r="J4" s="58"/>
+      <c r="K4" s="58"/>
+      <c r="L4" s="58"/>
+      <c r="M4" s="58"/>
+      <c r="N4" s="58"/>
+      <c r="O4" s="58"/>
+      <c r="P4" s="58"/>
+      <c r="Q4" s="58"/>
+      <c r="R4" s="58"/>
+      <c r="S4" s="58"/>
+      <c r="T4" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="U4" s="26">
+      <c r="U4" s="53">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="14.1" customHeight="1">
-      <c r="A5" s="36"/>
-      <c r="B5" s="36"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="40" t="s">
+    <row r="5" spans="1:22" ht="14.1" customHeight="1">
+      <c r="A5" s="43"/>
+      <c r="B5" s="43"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="41"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="37" t="s">
+      <c r="G5" s="61"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="37"/>
-      <c r="K5" s="37"/>
-      <c r="L5" s="37"/>
-      <c r="M5" s="37"/>
-      <c r="N5" s="37"/>
-      <c r="O5" s="37"/>
-      <c r="P5" s="37"/>
-      <c r="Q5" s="37"/>
-      <c r="R5" s="37"/>
-      <c r="S5" s="37"/>
-      <c r="T5" s="27"/>
-      <c r="U5" s="27"/>
-    </row>
-    <row r="6" spans="1:21" ht="31.5" customHeight="1">
-      <c r="A6" s="60"/>
-      <c r="B6" s="60"/>
-      <c r="C6" s="60"/>
-      <c r="D6" s="60"/>
-      <c r="E6" s="60"/>
-      <c r="F6" s="61" t="s">
+      <c r="J5" s="58"/>
+      <c r="K5" s="58"/>
+      <c r="L5" s="58"/>
+      <c r="M5" s="58"/>
+      <c r="N5" s="58"/>
+      <c r="O5" s="58"/>
+      <c r="P5" s="58"/>
+      <c r="Q5" s="58"/>
+      <c r="R5" s="58"/>
+      <c r="S5" s="58"/>
+      <c r="T5" s="55"/>
+      <c r="U5" s="55"/>
+    </row>
+    <row r="6" spans="1:22" ht="31.5" customHeight="1">
+      <c r="A6" s="44"/>
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="61"/>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="61"/>
-      <c r="L6" s="61"/>
-      <c r="M6" s="61"/>
-      <c r="N6" s="61"/>
-      <c r="O6" s="61"/>
-      <c r="P6" s="61"/>
-      <c r="Q6" s="61"/>
-      <c r="R6" s="61"/>
-      <c r="S6" s="61"/>
-      <c r="T6" s="20" t="s">
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="57"/>
+      <c r="L6" s="57"/>
+      <c r="M6" s="57"/>
+      <c r="N6" s="57"/>
+      <c r="O6" s="57"/>
+      <c r="P6" s="57"/>
+      <c r="Q6" s="57"/>
+      <c r="R6" s="57"/>
+      <c r="S6" s="57"/>
+      <c r="T6" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="U6" s="18">
+      <c r="U6" s="22">
         <v>46142</v>
       </c>
     </row>
-    <row r="7" spans="1:21" s="21" customFormat="1" ht="18" customHeight="1">
+    <row r="7" spans="1:22" s="18" customFormat="1" ht="18" customHeight="1">
       <c r="A7" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="73"/>
-      <c r="C7" s="74" t="s">
+      <c r="B7" s="67"/>
+      <c r="C7" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="74"/>
-      <c r="E7" s="74"/>
-      <c r="F7" s="75" t="s">
+      <c r="D7" s="68"/>
+      <c r="E7" s="68"/>
+      <c r="F7" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="75"/>
-      <c r="H7" s="67"/>
-      <c r="I7" s="67"/>
-      <c r="J7" s="67"/>
-      <c r="K7" s="67"/>
-      <c r="L7" s="67" t="s">
+      <c r="G7" s="69"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="M7" s="68"/>
-      <c r="N7" s="68"/>
-      <c r="O7" s="68"/>
-      <c r="P7" s="68"/>
-      <c r="Q7" s="67" t="s">
+      <c r="M7" s="42"/>
+      <c r="N7" s="42"/>
+      <c r="O7" s="42"/>
+      <c r="P7" s="42"/>
+      <c r="Q7" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="R7" s="68"/>
-      <c r="S7" s="68"/>
-      <c r="T7" s="69" t="s">
+      <c r="R7" s="42"/>
+      <c r="S7" s="42"/>
+      <c r="T7" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="U7" s="70"/>
-    </row>
-    <row r="8" spans="1:21" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="62"/>
-      <c r="B8" s="71" t="s">
+      <c r="U7" s="27"/>
+      <c r="V7" s="20"/>
+    </row>
+    <row r="8" spans="1:22" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A8" s="24"/>
+      <c r="B8" s="73" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="71"/>
-      <c r="D8" s="71"/>
-      <c r="E8" s="71"/>
-      <c r="F8" s="71"/>
-      <c r="G8" s="72"/>
-      <c r="H8" s="65" t="s">
+      <c r="C8" s="73"/>
+      <c r="D8" s="73"/>
+      <c r="E8" s="73"/>
+      <c r="F8" s="73"/>
+      <c r="G8" s="74"/>
+      <c r="H8" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="I8" s="63"/>
-      <c r="J8" s="63"/>
-      <c r="K8" s="63"/>
-      <c r="L8" s="63"/>
-      <c r="M8" s="64"/>
-      <c r="N8" s="65" t="s">
+      <c r="I8" s="71"/>
+      <c r="J8" s="71"/>
+      <c r="K8" s="71"/>
+      <c r="L8" s="71"/>
+      <c r="M8" s="72"/>
+      <c r="N8" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="O8" s="63"/>
-      <c r="P8" s="63"/>
-      <c r="Q8" s="63"/>
-      <c r="R8" s="63"/>
-      <c r="S8" s="64"/>
-      <c r="T8" s="34" t="s">
+      <c r="O8" s="71"/>
+      <c r="P8" s="71"/>
+      <c r="Q8" s="71"/>
+      <c r="R8" s="71"/>
+      <c r="S8" s="72"/>
+      <c r="T8" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="U8" s="34" t="s">
+      <c r="U8" s="40" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="16.5" customHeight="1">
+    <row r="9" spans="1:22" ht="16.5" customHeight="1">
       <c r="A9" s="16" t="s">
         <v>21</v>
       </c>
@@ -1727,180 +1700,180 @@
       <c r="S9" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="T9" s="35"/>
-      <c r="U9" s="35"/>
-    </row>
-    <row r="10" spans="1:21" ht="18" customHeight="1">
+      <c r="T9" s="41"/>
+      <c r="U9" s="41"/>
+    </row>
+    <row r="10" spans="1:22" ht="18" customHeight="1">
       <c r="A10" s="4">
         <v>1</v>
       </c>
       <c r="B10" s="14"/>
       <c r="C10" s="7"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
       <c r="G10" s="8"/>
       <c r="H10" s="14"/>
       <c r="I10" s="7"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="23"/>
+      <c r="L10" s="23"/>
       <c r="M10" s="8"/>
       <c r="N10" s="14"/>
       <c r="O10" s="7"/>
-      <c r="P10" s="17"/>
-      <c r="Q10" s="17"/>
-      <c r="R10" s="17"/>
+      <c r="P10" s="23"/>
+      <c r="Q10" s="23"/>
+      <c r="R10" s="23"/>
       <c r="S10" s="8"/>
       <c r="T10" s="12"/>
       <c r="U10" s="12"/>
     </row>
-    <row r="11" spans="1:21" ht="18" customHeight="1">
+    <row r="11" spans="1:22" ht="18" customHeight="1">
       <c r="A11" s="4">
         <v>2</v>
       </c>
       <c r="B11" s="14"/>
       <c r="C11" s="7"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
       <c r="G11" s="8"/>
       <c r="H11" s="14"/>
       <c r="I11" s="7"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
+      <c r="J11" s="23"/>
+      <c r="K11" s="23"/>
+      <c r="L11" s="23"/>
       <c r="M11" s="8"/>
       <c r="N11" s="14"/>
       <c r="O11" s="7"/>
-      <c r="P11" s="17"/>
-      <c r="Q11" s="17"/>
-      <c r="R11" s="17"/>
+      <c r="P11" s="23"/>
+      <c r="Q11" s="23"/>
+      <c r="R11" s="23"/>
       <c r="S11" s="8"/>
       <c r="T11" s="4"/>
       <c r="U11" s="4"/>
     </row>
-    <row r="12" spans="1:21" ht="18" customHeight="1">
+    <row r="12" spans="1:22" ht="18" customHeight="1">
       <c r="A12" s="4">
         <v>3</v>
       </c>
       <c r="B12" s="14"/>
       <c r="C12" s="7"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
       <c r="G12" s="8"/>
       <c r="H12" s="14"/>
       <c r="I12" s="7"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="17"/>
+      <c r="J12" s="23"/>
+      <c r="K12" s="23"/>
+      <c r="L12" s="23"/>
       <c r="M12" s="8"/>
       <c r="N12" s="14"/>
       <c r="O12" s="7"/>
-      <c r="P12" s="17"/>
-      <c r="Q12" s="17"/>
-      <c r="R12" s="17"/>
+      <c r="P12" s="23"/>
+      <c r="Q12" s="23"/>
+      <c r="R12" s="23"/>
       <c r="S12" s="8"/>
       <c r="T12" s="4"/>
       <c r="U12" s="4"/>
     </row>
-    <row r="13" spans="1:21" ht="18" customHeight="1">
+    <row r="13" spans="1:22" ht="18" customHeight="1">
       <c r="A13" s="4">
         <v>4</v>
       </c>
       <c r="B13" s="14"/>
       <c r="C13" s="7"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
       <c r="G13" s="8"/>
       <c r="H13" s="14"/>
       <c r="I13" s="7"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="17"/>
-      <c r="L13" s="17"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="23"/>
+      <c r="L13" s="23"/>
       <c r="M13" s="8"/>
       <c r="N13" s="14"/>
       <c r="O13" s="7"/>
-      <c r="P13" s="17"/>
-      <c r="Q13" s="17"/>
-      <c r="R13" s="17"/>
+      <c r="P13" s="23"/>
+      <c r="Q13" s="23"/>
+      <c r="R13" s="23"/>
       <c r="S13" s="8"/>
       <c r="T13" s="4"/>
       <c r="U13" s="4"/>
     </row>
-    <row r="14" spans="1:21" ht="18" customHeight="1">
+    <row r="14" spans="1:22" ht="18" customHeight="1">
       <c r="A14" s="4">
         <v>5</v>
       </c>
       <c r="B14" s="14"/>
       <c r="C14" s="7"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
       <c r="G14" s="8"/>
       <c r="H14" s="14"/>
       <c r="I14" s="7"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="17"/>
-      <c r="L14" s="17"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="23"/>
+      <c r="L14" s="23"/>
       <c r="M14" s="8"/>
       <c r="N14" s="14"/>
       <c r="O14" s="7"/>
-      <c r="P14" s="17"/>
-      <c r="Q14" s="17"/>
-      <c r="R14" s="17"/>
+      <c r="P14" s="23"/>
+      <c r="Q14" s="23"/>
+      <c r="R14" s="23"/>
       <c r="S14" s="8"/>
       <c r="T14" s="4"/>
       <c r="U14" s="4"/>
     </row>
-    <row r="15" spans="1:21" ht="18" customHeight="1">
+    <row r="15" spans="1:22" ht="18" customHeight="1">
       <c r="A15" s="4">
         <v>6</v>
       </c>
       <c r="B15" s="14"/>
       <c r="C15" s="7"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
       <c r="G15" s="8"/>
       <c r="H15" s="14"/>
       <c r="I15" s="7"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="17"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23"/>
+      <c r="L15" s="23"/>
       <c r="M15" s="8"/>
       <c r="N15" s="14"/>
       <c r="O15" s="7"/>
-      <c r="P15" s="17"/>
-      <c r="Q15" s="17"/>
-      <c r="R15" s="17"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
       <c r="S15" s="8"/>
       <c r="T15" s="4"/>
       <c r="U15" s="4"/>
     </row>
-    <row r="16" spans="1:21" ht="18" customHeight="1">
+    <row r="16" spans="1:22" ht="18" customHeight="1">
       <c r="A16" s="4">
         <v>7</v>
       </c>
       <c r="B16" s="14"/>
       <c r="C16" s="7"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
       <c r="G16" s="8"/>
       <c r="H16" s="14"/>
       <c r="I16" s="7"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="17"/>
-      <c r="L16" s="17"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="23"/>
+      <c r="L16" s="23"/>
       <c r="M16" s="8"/>
       <c r="N16" s="14"/>
       <c r="O16" s="7"/>
-      <c r="P16" s="17"/>
-      <c r="Q16" s="17"/>
-      <c r="R16" s="17"/>
+      <c r="P16" s="23"/>
+      <c r="Q16" s="23"/>
+      <c r="R16" s="23"/>
       <c r="S16" s="8"/>
       <c r="T16" s="4"/>
       <c r="U16" s="4"/>
@@ -1911,21 +1884,21 @@
       </c>
       <c r="B17" s="14"/>
       <c r="C17" s="7"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
       <c r="G17" s="8"/>
       <c r="H17" s="14"/>
       <c r="I17" s="7"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="17"/>
-      <c r="L17" s="17"/>
+      <c r="J17" s="23"/>
+      <c r="K17" s="23"/>
+      <c r="L17" s="23"/>
       <c r="M17" s="8"/>
       <c r="N17" s="14"/>
       <c r="O17" s="7"/>
-      <c r="P17" s="17"/>
-      <c r="Q17" s="17"/>
-      <c r="R17" s="17"/>
+      <c r="P17" s="23"/>
+      <c r="Q17" s="23"/>
+      <c r="R17" s="23"/>
       <c r="S17" s="8"/>
       <c r="T17" s="4"/>
       <c r="U17" s="4"/>
@@ -1936,21 +1909,21 @@
       </c>
       <c r="B18" s="14"/>
       <c r="C18" s="7"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
       <c r="G18" s="8"/>
       <c r="H18" s="14"/>
       <c r="I18" s="7"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="17"/>
-      <c r="L18" s="17"/>
+      <c r="J18" s="23"/>
+      <c r="K18" s="23"/>
+      <c r="L18" s="23"/>
       <c r="M18" s="8"/>
       <c r="N18" s="14"/>
       <c r="O18" s="7"/>
-      <c r="P18" s="17"/>
-      <c r="Q18" s="17"/>
-      <c r="R18" s="17"/>
+      <c r="P18" s="23"/>
+      <c r="Q18" s="23"/>
+      <c r="R18" s="23"/>
       <c r="S18" s="8"/>
       <c r="T18" s="4"/>
       <c r="U18" s="4"/>
@@ -1961,21 +1934,21 @@
       </c>
       <c r="B19" s="14"/>
       <c r="C19" s="7"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
       <c r="G19" s="8"/>
       <c r="H19" s="14"/>
       <c r="I19" s="7"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="17"/>
-      <c r="L19" s="17"/>
+      <c r="J19" s="23"/>
+      <c r="K19" s="23"/>
+      <c r="L19" s="23"/>
       <c r="M19" s="8"/>
       <c r="N19" s="14"/>
       <c r="O19" s="7"/>
-      <c r="P19" s="17"/>
-      <c r="Q19" s="17"/>
-      <c r="R19" s="17"/>
+      <c r="P19" s="23"/>
+      <c r="Q19" s="23"/>
+      <c r="R19" s="23"/>
       <c r="S19" s="8"/>
       <c r="T19" s="4"/>
       <c r="U19" s="4"/>
@@ -1986,21 +1959,21 @@
       </c>
       <c r="B20" s="14"/>
       <c r="C20" s="7"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
       <c r="G20" s="8"/>
       <c r="H20" s="14"/>
       <c r="I20" s="7"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="17"/>
-      <c r="L20" s="17"/>
+      <c r="J20" s="23"/>
+      <c r="K20" s="23"/>
+      <c r="L20" s="23"/>
       <c r="M20" s="8"/>
       <c r="N20" s="14"/>
       <c r="O20" s="7"/>
-      <c r="P20" s="17"/>
-      <c r="Q20" s="17"/>
-      <c r="R20" s="17"/>
+      <c r="P20" s="23"/>
+      <c r="Q20" s="23"/>
+      <c r="R20" s="23"/>
       <c r="S20" s="8"/>
       <c r="T20" s="4"/>
       <c r="U20" s="4"/>
@@ -2011,21 +1984,21 @@
       </c>
       <c r="B21" s="14"/>
       <c r="C21" s="7"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
       <c r="G21" s="8"/>
       <c r="H21" s="14"/>
       <c r="I21" s="7"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="17"/>
-      <c r="L21" s="17"/>
+      <c r="J21" s="23"/>
+      <c r="K21" s="23"/>
+      <c r="L21" s="23"/>
       <c r="M21" s="8"/>
       <c r="N21" s="14"/>
       <c r="O21" s="7"/>
-      <c r="P21" s="17"/>
-      <c r="Q21" s="17"/>
-      <c r="R21" s="17"/>
+      <c r="P21" s="23"/>
+      <c r="Q21" s="23"/>
+      <c r="R21" s="23"/>
       <c r="S21" s="8"/>
       <c r="T21" s="4"/>
       <c r="U21" s="4"/>
@@ -2036,21 +2009,21 @@
       </c>
       <c r="B22" s="14"/>
       <c r="C22" s="7"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
       <c r="G22" s="8"/>
       <c r="H22" s="14"/>
       <c r="I22" s="7"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="17"/>
-      <c r="L22" s="17"/>
+      <c r="J22" s="23"/>
+      <c r="K22" s="23"/>
+      <c r="L22" s="23"/>
       <c r="M22" s="8"/>
       <c r="N22" s="14"/>
       <c r="O22" s="7"/>
-      <c r="P22" s="17"/>
-      <c r="Q22" s="17"/>
-      <c r="R22" s="17"/>
+      <c r="P22" s="23"/>
+      <c r="Q22" s="23"/>
+      <c r="R22" s="23"/>
       <c r="S22" s="8"/>
       <c r="T22" s="4"/>
       <c r="U22" s="4"/>
@@ -2061,21 +2034,21 @@
       </c>
       <c r="B23" s="14"/>
       <c r="C23" s="7"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
       <c r="G23" s="8"/>
       <c r="H23" s="14"/>
       <c r="I23" s="7"/>
-      <c r="J23" s="17"/>
-      <c r="K23" s="17"/>
-      <c r="L23" s="17"/>
+      <c r="J23" s="23"/>
+      <c r="K23" s="23"/>
+      <c r="L23" s="23"/>
       <c r="M23" s="8"/>
       <c r="N23" s="14"/>
       <c r="O23" s="7"/>
-      <c r="P23" s="17"/>
-      <c r="Q23" s="17"/>
-      <c r="R23" s="17"/>
+      <c r="P23" s="23"/>
+      <c r="Q23" s="23"/>
+      <c r="R23" s="23"/>
       <c r="S23" s="8"/>
       <c r="T23" s="4"/>
       <c r="U23" s="4"/>
@@ -2086,21 +2059,21 @@
       </c>
       <c r="B24" s="14"/>
       <c r="C24" s="7"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="23"/>
       <c r="G24" s="8"/>
       <c r="H24" s="14"/>
       <c r="I24" s="7"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="17"/>
-      <c r="L24" s="17"/>
+      <c r="J24" s="23"/>
+      <c r="K24" s="23"/>
+      <c r="L24" s="23"/>
       <c r="M24" s="8"/>
       <c r="N24" s="14"/>
       <c r="O24" s="7"/>
-      <c r="P24" s="17"/>
-      <c r="Q24" s="17"/>
-      <c r="R24" s="17"/>
+      <c r="P24" s="23"/>
+      <c r="Q24" s="23"/>
+      <c r="R24" s="23"/>
       <c r="S24" s="8"/>
       <c r="T24" s="4"/>
       <c r="U24" s="4"/>
@@ -2111,21 +2084,21 @@
       </c>
       <c r="B25" s="14"/>
       <c r="C25" s="7"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="23"/>
       <c r="G25" s="8"/>
       <c r="H25" s="14"/>
       <c r="I25" s="7"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="17"/>
-      <c r="L25" s="17"/>
+      <c r="J25" s="23"/>
+      <c r="K25" s="23"/>
+      <c r="L25" s="23"/>
       <c r="M25" s="8"/>
       <c r="N25" s="14"/>
       <c r="O25" s="7"/>
-      <c r="P25" s="17"/>
-      <c r="Q25" s="17"/>
-      <c r="R25" s="17"/>
+      <c r="P25" s="23"/>
+      <c r="Q25" s="23"/>
+      <c r="R25" s="23"/>
       <c r="S25" s="8"/>
       <c r="T25" s="4"/>
       <c r="U25" s="4"/>
@@ -2136,21 +2109,21 @@
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="7"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="23"/>
       <c r="G26" s="8"/>
       <c r="H26" s="14"/>
       <c r="I26" s="7"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="17"/>
-      <c r="L26" s="17"/>
+      <c r="J26" s="23"/>
+      <c r="K26" s="23"/>
+      <c r="L26" s="23"/>
       <c r="M26" s="8"/>
       <c r="N26" s="14"/>
       <c r="O26" s="7"/>
-      <c r="P26" s="17"/>
-      <c r="Q26" s="17"/>
-      <c r="R26" s="17"/>
+      <c r="P26" s="23"/>
+      <c r="Q26" s="23"/>
+      <c r="R26" s="23"/>
       <c r="S26" s="8"/>
       <c r="T26" s="4"/>
       <c r="U26" s="4"/>
@@ -2161,21 +2134,21 @@
       </c>
       <c r="B27" s="14"/>
       <c r="C27" s="7"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
       <c r="G27" s="8"/>
       <c r="H27" s="14"/>
       <c r="I27" s="7"/>
-      <c r="J27" s="17"/>
-      <c r="K27" s="17"/>
-      <c r="L27" s="17"/>
+      <c r="J27" s="23"/>
+      <c r="K27" s="23"/>
+      <c r="L27" s="23"/>
       <c r="M27" s="8"/>
       <c r="N27" s="14"/>
       <c r="O27" s="7"/>
-      <c r="P27" s="17"/>
-      <c r="Q27" s="17"/>
-      <c r="R27" s="17"/>
+      <c r="P27" s="23"/>
+      <c r="Q27" s="23"/>
+      <c r="R27" s="23"/>
       <c r="S27" s="8"/>
       <c r="T27" s="4"/>
       <c r="U27" s="4"/>
@@ -2186,21 +2159,21 @@
       </c>
       <c r="B28" s="14"/>
       <c r="C28" s="7"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
       <c r="G28" s="8"/>
       <c r="H28" s="14"/>
       <c r="I28" s="7"/>
-      <c r="J28" s="17"/>
-      <c r="K28" s="17"/>
-      <c r="L28" s="17"/>
+      <c r="J28" s="23"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="23"/>
       <c r="M28" s="8"/>
       <c r="N28" s="14"/>
       <c r="O28" s="7"/>
-      <c r="P28" s="17"/>
-      <c r="Q28" s="17"/>
-      <c r="R28" s="17"/>
+      <c r="P28" s="23"/>
+      <c r="Q28" s="23"/>
+      <c r="R28" s="23"/>
       <c r="S28" s="8"/>
       <c r="T28" s="4"/>
       <c r="U28" s="4"/>
@@ -2211,21 +2184,21 @@
       </c>
       <c r="B29" s="14"/>
       <c r="C29" s="7"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
+      <c r="D29" s="23"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="23"/>
       <c r="G29" s="8"/>
       <c r="H29" s="14"/>
       <c r="I29" s="7"/>
-      <c r="J29" s="17"/>
-      <c r="K29" s="17"/>
-      <c r="L29" s="17"/>
+      <c r="J29" s="23"/>
+      <c r="K29" s="23"/>
+      <c r="L29" s="23"/>
       <c r="M29" s="8"/>
       <c r="N29" s="14"/>
       <c r="O29" s="7"/>
-      <c r="P29" s="17"/>
-      <c r="Q29" s="17"/>
-      <c r="R29" s="17"/>
+      <c r="P29" s="23"/>
+      <c r="Q29" s="23"/>
+      <c r="R29" s="23"/>
       <c r="S29" s="8"/>
       <c r="T29" s="4"/>
       <c r="U29" s="4"/>
@@ -2236,21 +2209,21 @@
       </c>
       <c r="B30" s="14"/>
       <c r="C30" s="7"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
+      <c r="D30" s="23"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="23"/>
       <c r="G30" s="8"/>
       <c r="H30" s="14"/>
       <c r="I30" s="7"/>
-      <c r="J30" s="17"/>
-      <c r="K30" s="17"/>
-      <c r="L30" s="17"/>
+      <c r="J30" s="23"/>
+      <c r="K30" s="23"/>
+      <c r="L30" s="23"/>
       <c r="M30" s="8"/>
       <c r="N30" s="14"/>
       <c r="O30" s="7"/>
-      <c r="P30" s="17"/>
-      <c r="Q30" s="17"/>
-      <c r="R30" s="17"/>
+      <c r="P30" s="23"/>
+      <c r="Q30" s="23"/>
+      <c r="R30" s="23"/>
       <c r="S30" s="8"/>
       <c r="T30" s="4"/>
       <c r="U30" s="4"/>
@@ -2261,21 +2234,21 @@
       </c>
       <c r="B31" s="14"/>
       <c r="C31" s="7"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23"/>
       <c r="G31" s="8"/>
       <c r="H31" s="14"/>
       <c r="I31" s="7"/>
-      <c r="J31" s="17"/>
-      <c r="K31" s="17"/>
-      <c r="L31" s="17"/>
+      <c r="J31" s="23"/>
+      <c r="K31" s="23"/>
+      <c r="L31" s="23"/>
       <c r="M31" s="8"/>
       <c r="N31" s="14"/>
       <c r="O31" s="7"/>
-      <c r="P31" s="17"/>
-      <c r="Q31" s="17"/>
-      <c r="R31" s="17"/>
+      <c r="P31" s="23"/>
+      <c r="Q31" s="23"/>
+      <c r="R31" s="23"/>
       <c r="S31" s="8"/>
       <c r="T31" s="4"/>
       <c r="U31" s="4"/>
@@ -2286,21 +2259,21 @@
       </c>
       <c r="B32" s="14"/>
       <c r="C32" s="7"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
+      <c r="D32" s="23"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="23"/>
       <c r="G32" s="8"/>
       <c r="H32" s="14"/>
       <c r="I32" s="7"/>
-      <c r="J32" s="17"/>
-      <c r="K32" s="17"/>
-      <c r="L32" s="17"/>
+      <c r="J32" s="23"/>
+      <c r="K32" s="23"/>
+      <c r="L32" s="23"/>
       <c r="M32" s="8"/>
       <c r="N32" s="14"/>
       <c r="O32" s="7"/>
-      <c r="P32" s="17"/>
-      <c r="Q32" s="17"/>
-      <c r="R32" s="17"/>
+      <c r="P32" s="23"/>
+      <c r="Q32" s="23"/>
+      <c r="R32" s="23"/>
       <c r="S32" s="8"/>
       <c r="T32" s="4"/>
       <c r="U32" s="4"/>
@@ -2311,21 +2284,21 @@
       </c>
       <c r="B33" s="14"/>
       <c r="C33" s="7"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="23"/>
       <c r="G33" s="8"/>
       <c r="H33" s="14"/>
       <c r="I33" s="7"/>
-      <c r="J33" s="17"/>
-      <c r="K33" s="17"/>
-      <c r="L33" s="17"/>
+      <c r="J33" s="23"/>
+      <c r="K33" s="23"/>
+      <c r="L33" s="23"/>
       <c r="M33" s="8"/>
       <c r="N33" s="14"/>
       <c r="O33" s="7"/>
-      <c r="P33" s="17"/>
-      <c r="Q33" s="17"/>
-      <c r="R33" s="17"/>
+      <c r="P33" s="23"/>
+      <c r="Q33" s="23"/>
+      <c r="R33" s="23"/>
       <c r="S33" s="8"/>
       <c r="T33" s="4"/>
       <c r="U33" s="4"/>
@@ -2336,21 +2309,21 @@
       </c>
       <c r="B34" s="14"/>
       <c r="C34" s="7"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="23"/>
       <c r="G34" s="8"/>
       <c r="H34" s="14"/>
       <c r="I34" s="7"/>
-      <c r="J34" s="17"/>
-      <c r="K34" s="17"/>
-      <c r="L34" s="17"/>
+      <c r="J34" s="23"/>
+      <c r="K34" s="23"/>
+      <c r="L34" s="23"/>
       <c r="M34" s="8"/>
       <c r="N34" s="14"/>
       <c r="O34" s="7"/>
-      <c r="P34" s="17"/>
-      <c r="Q34" s="17"/>
-      <c r="R34" s="17"/>
+      <c r="P34" s="23"/>
+      <c r="Q34" s="23"/>
+      <c r="R34" s="23"/>
       <c r="S34" s="8"/>
       <c r="T34" s="4"/>
       <c r="U34" s="4"/>
@@ -2361,21 +2334,21 @@
       </c>
       <c r="B35" s="14"/>
       <c r="C35" s="7"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="23"/>
       <c r="G35" s="8"/>
       <c r="H35" s="14"/>
       <c r="I35" s="7"/>
-      <c r="J35" s="17"/>
-      <c r="K35" s="17"/>
-      <c r="L35" s="17"/>
+      <c r="J35" s="23"/>
+      <c r="K35" s="23"/>
+      <c r="L35" s="23"/>
       <c r="M35" s="8"/>
       <c r="N35" s="14"/>
       <c r="O35" s="7"/>
-      <c r="P35" s="17"/>
-      <c r="Q35" s="17"/>
-      <c r="R35" s="17"/>
+      <c r="P35" s="23"/>
+      <c r="Q35" s="23"/>
+      <c r="R35" s="23"/>
       <c r="S35" s="8"/>
       <c r="T35" s="4"/>
       <c r="U35" s="4"/>
@@ -2386,21 +2359,21 @@
       </c>
       <c r="B36" s="14"/>
       <c r="C36" s="7"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="17"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="23"/>
       <c r="G36" s="8"/>
       <c r="H36" s="14"/>
       <c r="I36" s="7"/>
-      <c r="J36" s="17"/>
-      <c r="K36" s="17"/>
-      <c r="L36" s="17"/>
+      <c r="J36" s="23"/>
+      <c r="K36" s="23"/>
+      <c r="L36" s="23"/>
       <c r="M36" s="8"/>
       <c r="N36" s="14"/>
       <c r="O36" s="7"/>
-      <c r="P36" s="17"/>
-      <c r="Q36" s="17"/>
-      <c r="R36" s="17"/>
+      <c r="P36" s="23"/>
+      <c r="Q36" s="23"/>
+      <c r="R36" s="23"/>
       <c r="S36" s="8"/>
       <c r="T36" s="4"/>
       <c r="U36" s="4"/>
@@ -2411,21 +2384,21 @@
       </c>
       <c r="B37" s="14"/>
       <c r="C37" s="7"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="17"/>
-      <c r="F37" s="17"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="23"/>
       <c r="G37" s="8"/>
       <c r="H37" s="14"/>
       <c r="I37" s="7"/>
-      <c r="J37" s="17"/>
-      <c r="K37" s="17"/>
-      <c r="L37" s="17"/>
+      <c r="J37" s="23"/>
+      <c r="K37" s="23"/>
+      <c r="L37" s="23"/>
       <c r="M37" s="8"/>
       <c r="N37" s="14"/>
       <c r="O37" s="7"/>
-      <c r="P37" s="17"/>
-      <c r="Q37" s="17"/>
-      <c r="R37" s="17"/>
+      <c r="P37" s="23"/>
+      <c r="Q37" s="23"/>
+      <c r="R37" s="23"/>
       <c r="S37" s="8"/>
       <c r="T37" s="4"/>
       <c r="U37" s="4"/>
@@ -2436,21 +2409,21 @@
       </c>
       <c r="B38" s="14"/>
       <c r="C38" s="7"/>
-      <c r="D38" s="17"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="17"/>
+      <c r="D38" s="23"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="23"/>
       <c r="G38" s="8"/>
       <c r="H38" s="14"/>
       <c r="I38" s="7"/>
-      <c r="J38" s="17"/>
-      <c r="K38" s="17"/>
-      <c r="L38" s="17"/>
+      <c r="J38" s="23"/>
+      <c r="K38" s="23"/>
+      <c r="L38" s="23"/>
       <c r="M38" s="8"/>
       <c r="N38" s="14"/>
       <c r="O38" s="7"/>
-      <c r="P38" s="17"/>
-      <c r="Q38" s="17"/>
-      <c r="R38" s="17"/>
+      <c r="P38" s="23"/>
+      <c r="Q38" s="23"/>
+      <c r="R38" s="23"/>
       <c r="S38" s="8"/>
       <c r="T38" s="4"/>
       <c r="U38" s="4"/>
@@ -2461,21 +2434,21 @@
       </c>
       <c r="B39" s="14"/>
       <c r="C39" s="7"/>
-      <c r="D39" s="17"/>
-      <c r="E39" s="17"/>
-      <c r="F39" s="17"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="23"/>
+      <c r="F39" s="23"/>
       <c r="G39" s="8"/>
       <c r="H39" s="14"/>
       <c r="I39" s="7"/>
-      <c r="J39" s="17"/>
-      <c r="K39" s="17"/>
-      <c r="L39" s="17"/>
+      <c r="J39" s="23"/>
+      <c r="K39" s="23"/>
+      <c r="L39" s="23"/>
       <c r="M39" s="8"/>
       <c r="N39" s="14"/>
       <c r="O39" s="7"/>
-      <c r="P39" s="17"/>
-      <c r="Q39" s="17"/>
-      <c r="R39" s="17"/>
+      <c r="P39" s="23"/>
+      <c r="Q39" s="23"/>
+      <c r="R39" s="23"/>
       <c r="S39" s="8"/>
       <c r="T39" s="4"/>
       <c r="U39" s="4"/>
@@ -2519,438 +2492,499 @@
       </c>
     </row>
     <row r="43" spans="1:21">
-      <c r="A43" s="19" t="s">
+      <c r="A43" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B43" s="29" t="s">
+      <c r="B43" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="C43" s="29"/>
-      <c r="D43" s="29"/>
-      <c r="E43" s="29"/>
-      <c r="F43" s="29"/>
-      <c r="G43" s="29"/>
-      <c r="H43" s="29"/>
-      <c r="I43" s="29"/>
-      <c r="J43" s="29"/>
-      <c r="K43" s="29"/>
-      <c r="L43" s="29"/>
-      <c r="M43" s="29"/>
-      <c r="N43" s="29"/>
-      <c r="O43" s="29"/>
-      <c r="P43" s="29"/>
-      <c r="Q43" s="29"/>
-      <c r="R43" s="29"/>
-      <c r="S43" s="29"/>
-      <c r="T43" s="29"/>
-      <c r="U43" s="29"/>
+      <c r="C43" s="45"/>
+      <c r="D43" s="45"/>
+      <c r="E43" s="45"/>
+      <c r="F43" s="45"/>
+      <c r="G43" s="45"/>
+      <c r="H43" s="45"/>
+      <c r="I43" s="45"/>
+      <c r="J43" s="45"/>
+      <c r="K43" s="45"/>
+      <c r="L43" s="45"/>
+      <c r="M43" s="45"/>
+      <c r="N43" s="45"/>
+      <c r="O43" s="45"/>
+      <c r="P43" s="45"/>
+      <c r="Q43" s="45"/>
+      <c r="R43" s="45"/>
+      <c r="S43" s="45"/>
+      <c r="T43" s="45"/>
+      <c r="U43" s="45"/>
     </row>
     <row r="44" spans="1:21">
-      <c r="A44" s="19" t="s">
+      <c r="A44" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="B44" s="33" t="s">
+      <c r="B44" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="C44" s="33"/>
-      <c r="D44" s="33"/>
-      <c r="E44" s="33"/>
-      <c r="F44" s="33"/>
-      <c r="G44" s="33"/>
-      <c r="H44" s="33"/>
-      <c r="I44" s="33"/>
-      <c r="J44" s="33"/>
-      <c r="K44" s="33"/>
-      <c r="L44" s="33"/>
-      <c r="M44" s="33"/>
-      <c r="N44" s="33"/>
-      <c r="O44" s="33"/>
-      <c r="P44" s="33"/>
-      <c r="Q44" s="33"/>
-      <c r="R44" s="33"/>
-      <c r="S44" s="33"/>
-      <c r="T44" s="33"/>
-      <c r="U44" s="33"/>
+      <c r="C44" s="56"/>
+      <c r="D44" s="56"/>
+      <c r="E44" s="56"/>
+      <c r="F44" s="56"/>
+      <c r="G44" s="56"/>
+      <c r="H44" s="56"/>
+      <c r="I44" s="56"/>
+      <c r="J44" s="56"/>
+      <c r="K44" s="56"/>
+      <c r="L44" s="56"/>
+      <c r="M44" s="56"/>
+      <c r="N44" s="56"/>
+      <c r="O44" s="56"/>
+      <c r="P44" s="56"/>
+      <c r="Q44" s="56"/>
+      <c r="R44" s="56"/>
+      <c r="S44" s="56"/>
+      <c r="T44" s="56"/>
+      <c r="U44" s="56"/>
     </row>
     <row r="45" spans="1:21">
-      <c r="A45" s="19" t="s">
+      <c r="A45" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B45" s="29" t="s">
+      <c r="B45" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="C45" s="29"/>
-      <c r="D45" s="29"/>
-      <c r="E45" s="29"/>
-      <c r="F45" s="29"/>
-      <c r="G45" s="29"/>
-      <c r="H45" s="29"/>
-      <c r="I45" s="29"/>
-      <c r="J45" s="29"/>
-      <c r="K45" s="29"/>
-      <c r="L45" s="29"/>
-      <c r="M45" s="29"/>
-      <c r="N45" s="29"/>
-      <c r="O45" s="29"/>
-      <c r="P45" s="29"/>
-      <c r="Q45" s="29"/>
-      <c r="R45" s="29"/>
-      <c r="S45" s="29"/>
-      <c r="T45" s="29"/>
-      <c r="U45" s="29"/>
+      <c r="C45" s="45"/>
+      <c r="D45" s="45"/>
+      <c r="E45" s="45"/>
+      <c r="F45" s="45"/>
+      <c r="G45" s="45"/>
+      <c r="H45" s="45"/>
+      <c r="I45" s="45"/>
+      <c r="J45" s="45"/>
+      <c r="K45" s="45"/>
+      <c r="L45" s="45"/>
+      <c r="M45" s="45"/>
+      <c r="N45" s="45"/>
+      <c r="O45" s="45"/>
+      <c r="P45" s="45"/>
+      <c r="Q45" s="45"/>
+      <c r="R45" s="45"/>
+      <c r="S45" s="45"/>
+      <c r="T45" s="45"/>
+      <c r="U45" s="45"/>
     </row>
     <row r="46" spans="1:21">
-      <c r="A46" s="19" t="s">
+      <c r="A46" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="B46" s="29" t="s">
+      <c r="B46" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="C46" s="29"/>
-      <c r="D46" s="29"/>
-      <c r="E46" s="29"/>
-      <c r="F46" s="29"/>
-      <c r="G46" s="29"/>
-      <c r="H46" s="29"/>
-      <c r="I46" s="29"/>
-      <c r="J46" s="29"/>
-      <c r="K46" s="29"/>
-      <c r="L46" s="29"/>
-      <c r="M46" s="29"/>
-      <c r="N46" s="29"/>
-      <c r="O46" s="29"/>
-      <c r="P46" s="29"/>
-      <c r="Q46" s="29"/>
-      <c r="R46" s="29"/>
-      <c r="S46" s="29"/>
-      <c r="T46" s="29"/>
-      <c r="U46" s="29"/>
+      <c r="C46" s="45"/>
+      <c r="D46" s="45"/>
+      <c r="E46" s="45"/>
+      <c r="F46" s="45"/>
+      <c r="G46" s="45"/>
+      <c r="H46" s="45"/>
+      <c r="I46" s="45"/>
+      <c r="J46" s="45"/>
+      <c r="K46" s="45"/>
+      <c r="L46" s="45"/>
+      <c r="M46" s="45"/>
+      <c r="N46" s="45"/>
+      <c r="O46" s="45"/>
+      <c r="P46" s="45"/>
+      <c r="Q46" s="45"/>
+      <c r="R46" s="45"/>
+      <c r="S46" s="45"/>
+      <c r="T46" s="45"/>
+      <c r="U46" s="45"/>
     </row>
     <row r="47" spans="1:21">
-      <c r="A47" s="19" t="s">
+      <c r="A47" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="B47" s="29" t="s">
+      <c r="B47" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="C47" s="29"/>
-      <c r="D47" s="29"/>
-      <c r="E47" s="29"/>
-      <c r="F47" s="29"/>
-      <c r="G47" s="29"/>
-      <c r="H47" s="29"/>
-      <c r="I47" s="29"/>
-      <c r="J47" s="29"/>
-      <c r="K47" s="29"/>
-      <c r="L47" s="29"/>
-      <c r="M47" s="29"/>
-      <c r="N47" s="29"/>
-      <c r="O47" s="29"/>
-      <c r="P47" s="29"/>
-      <c r="Q47" s="29"/>
-      <c r="R47" s="29"/>
-      <c r="S47" s="29"/>
-      <c r="T47" s="29"/>
-      <c r="U47" s="29"/>
+      <c r="C47" s="45"/>
+      <c r="D47" s="45"/>
+      <c r="E47" s="45"/>
+      <c r="F47" s="45"/>
+      <c r="G47" s="45"/>
+      <c r="H47" s="45"/>
+      <c r="I47" s="45"/>
+      <c r="J47" s="45"/>
+      <c r="K47" s="45"/>
+      <c r="L47" s="45"/>
+      <c r="M47" s="45"/>
+      <c r="N47" s="45"/>
+      <c r="O47" s="45"/>
+      <c r="P47" s="45"/>
+      <c r="Q47" s="45"/>
+      <c r="R47" s="45"/>
+      <c r="S47" s="45"/>
+      <c r="T47" s="45"/>
+      <c r="U47" s="45"/>
     </row>
     <row r="48" spans="1:21">
-      <c r="A48" s="19" t="s">
+      <c r="A48" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="B48" s="29" t="s">
+      <c r="B48" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="C48" s="29"/>
-      <c r="D48" s="29"/>
-      <c r="E48" s="29"/>
-      <c r="F48" s="29"/>
-      <c r="G48" s="29"/>
-      <c r="H48" s="29"/>
-      <c r="I48" s="29"/>
-      <c r="J48" s="29"/>
-      <c r="K48" s="29"/>
-      <c r="L48" s="29"/>
-      <c r="M48" s="29"/>
-      <c r="N48" s="29"/>
-      <c r="O48" s="29"/>
-      <c r="P48" s="29"/>
-      <c r="Q48" s="29"/>
-      <c r="R48" s="29"/>
-      <c r="S48" s="29"/>
-      <c r="T48" s="29"/>
-      <c r="U48" s="29"/>
+      <c r="C48" s="45"/>
+      <c r="D48" s="45"/>
+      <c r="E48" s="45"/>
+      <c r="F48" s="45"/>
+      <c r="G48" s="45"/>
+      <c r="H48" s="45"/>
+      <c r="I48" s="45"/>
+      <c r="J48" s="45"/>
+      <c r="K48" s="45"/>
+      <c r="L48" s="45"/>
+      <c r="M48" s="45"/>
+      <c r="N48" s="45"/>
+      <c r="O48" s="45"/>
+      <c r="P48" s="45"/>
+      <c r="Q48" s="45"/>
+      <c r="R48" s="45"/>
+      <c r="S48" s="45"/>
+      <c r="T48" s="45"/>
+      <c r="U48" s="45"/>
     </row>
     <row r="49" spans="1:21" ht="30" customHeight="1">
-      <c r="A49" s="19" t="s">
+      <c r="A49" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="B49" s="30" t="s">
+      <c r="B49" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="C49" s="30"/>
-      <c r="D49" s="30"/>
-      <c r="E49" s="30"/>
-      <c r="F49" s="30"/>
-      <c r="G49" s="30"/>
-      <c r="H49" s="30"/>
-      <c r="I49" s="30"/>
-      <c r="J49" s="30"/>
-      <c r="K49" s="30"/>
-      <c r="L49" s="30"/>
-      <c r="M49" s="30"/>
-      <c r="N49" s="30"/>
-      <c r="O49" s="30"/>
-      <c r="P49" s="30"/>
-      <c r="Q49" s="30"/>
-      <c r="R49" s="30"/>
-      <c r="S49" s="30"/>
-      <c r="T49" s="30"/>
-      <c r="U49" s="30"/>
+      <c r="C49" s="46"/>
+      <c r="D49" s="46"/>
+      <c r="E49" s="46"/>
+      <c r="F49" s="46"/>
+      <c r="G49" s="46"/>
+      <c r="H49" s="46"/>
+      <c r="I49" s="46"/>
+      <c r="J49" s="46"/>
+      <c r="K49" s="46"/>
+      <c r="L49" s="46"/>
+      <c r="M49" s="46"/>
+      <c r="N49" s="46"/>
+      <c r="O49" s="46"/>
+      <c r="P49" s="46"/>
+      <c r="Q49" s="46"/>
+      <c r="R49" s="46"/>
+      <c r="S49" s="46"/>
+      <c r="T49" s="46"/>
+      <c r="U49" s="46"/>
     </row>
     <row r="50" spans="1:21">
-      <c r="A50" s="19" t="s">
+      <c r="A50" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="B50" s="31" t="s">
+      <c r="B50" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="C50" s="31"/>
-      <c r="D50" s="31"/>
-      <c r="E50" s="31"/>
-      <c r="F50" s="31"/>
-      <c r="G50" s="31"/>
-      <c r="H50" s="31"/>
-      <c r="I50" s="31"/>
-      <c r="J50" s="31"/>
-      <c r="K50" s="31"/>
-      <c r="L50" s="31"/>
-      <c r="M50" s="31"/>
-      <c r="N50" s="31"/>
-      <c r="O50" s="31"/>
-      <c r="P50" s="31"/>
-      <c r="Q50" s="31"/>
-      <c r="R50" s="31"/>
-      <c r="S50" s="31"/>
-      <c r="T50" s="31"/>
-      <c r="U50" s="31"/>
+      <c r="C50" s="47"/>
+      <c r="D50" s="47"/>
+      <c r="E50" s="47"/>
+      <c r="F50" s="47"/>
+      <c r="G50" s="47"/>
+      <c r="H50" s="47"/>
+      <c r="I50" s="47"/>
+      <c r="J50" s="47"/>
+      <c r="K50" s="47"/>
+      <c r="L50" s="47"/>
+      <c r="M50" s="47"/>
+      <c r="N50" s="47"/>
+      <c r="O50" s="47"/>
+      <c r="P50" s="47"/>
+      <c r="Q50" s="47"/>
+      <c r="R50" s="47"/>
+      <c r="S50" s="47"/>
+      <c r="T50" s="47"/>
+      <c r="U50" s="47"/>
     </row>
     <row r="51" spans="1:21">
-      <c r="A51" s="19" t="s">
+      <c r="A51" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="B51" s="28" t="s">
+      <c r="B51" s="48" t="s">
         <v>48</v>
       </c>
-      <c r="C51" s="28"/>
-      <c r="D51" s="28"/>
-      <c r="E51" s="28"/>
-      <c r="F51" s="28"/>
-      <c r="G51" s="28"/>
-      <c r="H51" s="28"/>
-      <c r="I51" s="28"/>
-      <c r="J51" s="28"/>
-      <c r="K51" s="28"/>
-      <c r="L51" s="28"/>
-      <c r="M51" s="28"/>
-      <c r="N51" s="28"/>
-      <c r="O51" s="28"/>
-      <c r="P51" s="28"/>
-      <c r="Q51" s="28"/>
-      <c r="R51" s="28"/>
-      <c r="S51" s="28"/>
-      <c r="T51" s="28"/>
-      <c r="U51" s="28"/>
-    </row>
-    <row r="52" spans="1:21" ht="15" customHeight="1">
-      <c r="A52" s="19"/>
-      <c r="B52" s="32"/>
-      <c r="C52" s="32"/>
-      <c r="D52" s="32"/>
-      <c r="E52" s="32"/>
-      <c r="F52" s="32"/>
-      <c r="G52" s="32"/>
-      <c r="H52" s="32"/>
-      <c r="I52" s="32"/>
-      <c r="J52" s="32"/>
-      <c r="K52" s="32"/>
-      <c r="L52" s="32"/>
-      <c r="M52" s="32"/>
-      <c r="N52" s="32"/>
-      <c r="O52" s="32"/>
-      <c r="P52" s="32"/>
-      <c r="Q52" s="32"/>
-      <c r="R52" s="32"/>
-      <c r="S52" s="32"/>
-      <c r="T52" s="32"/>
-      <c r="U52" s="32"/>
-    </row>
-    <row r="53" spans="1:21" ht="15" customHeight="1">
+      <c r="C51" s="48"/>
+      <c r="D51" s="48"/>
+      <c r="E51" s="48"/>
+      <c r="F51" s="48"/>
+      <c r="G51" s="48"/>
+      <c r="H51" s="48"/>
+      <c r="I51" s="48"/>
+      <c r="J51" s="48"/>
+      <c r="K51" s="48"/>
+      <c r="L51" s="48"/>
+      <c r="M51" s="48"/>
+      <c r="N51" s="48"/>
+      <c r="O51" s="48"/>
+      <c r="P51" s="48"/>
+      <c r="Q51" s="48"/>
+      <c r="R51" s="48"/>
+      <c r="S51" s="48"/>
+      <c r="T51" s="48"/>
+      <c r="U51" s="48"/>
+    </row>
+    <row r="52" spans="1:21">
+      <c r="A52" s="38"/>
+      <c r="B52" s="38"/>
+      <c r="C52" s="38"/>
+      <c r="D52" s="38"/>
+      <c r="E52" s="38"/>
+      <c r="F52" s="38"/>
+      <c r="G52" s="38"/>
+      <c r="H52" s="38"/>
+      <c r="I52" s="38"/>
+      <c r="J52" s="38"/>
+      <c r="K52" s="38"/>
+      <c r="L52" s="38"/>
+      <c r="M52" s="38"/>
+      <c r="N52" s="38"/>
+      <c r="O52" s="38"/>
+      <c r="P52" s="38"/>
+      <c r="Q52" s="38"/>
+      <c r="R52" s="38"/>
+      <c r="S52" s="38"/>
+      <c r="T52" s="38"/>
+      <c r="U52" s="38"/>
+    </row>
+    <row r="53" spans="1:21">
       <c r="A53" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B53" s="28" t="s">
+      <c r="B53" s="48" t="s">
         <v>50</v>
       </c>
-      <c r="C53" s="28"/>
-      <c r="D53" s="28"/>
-      <c r="E53" s="28"/>
-      <c r="F53" s="28"/>
-      <c r="G53" s="28"/>
-      <c r="H53" s="28"/>
-      <c r="I53" s="28"/>
-      <c r="J53" s="28"/>
-      <c r="K53" s="28"/>
-      <c r="L53" s="28"/>
-      <c r="M53" s="28"/>
-      <c r="N53" s="28"/>
-      <c r="O53" s="28"/>
-      <c r="P53" s="28"/>
-      <c r="Q53" s="28"/>
-      <c r="R53" s="28"/>
-      <c r="S53" s="28"/>
-      <c r="T53" s="28"/>
-      <c r="U53" s="28"/>
-    </row>
-    <row r="54" spans="1:21" ht="15" customHeight="1"/>
+      <c r="C53" s="48"/>
+      <c r="D53" s="48"/>
+      <c r="E53" s="48"/>
+      <c r="F53" s="48"/>
+      <c r="G53" s="48"/>
+      <c r="H53" s="48"/>
+      <c r="I53" s="48"/>
+      <c r="J53" s="48"/>
+      <c r="K53" s="48"/>
+      <c r="L53" s="48"/>
+      <c r="M53" s="48"/>
+      <c r="N53" s="48"/>
+      <c r="O53" s="48"/>
+      <c r="P53" s="48"/>
+      <c r="Q53" s="48"/>
+      <c r="R53" s="48"/>
+      <c r="S53" s="48"/>
+      <c r="T53" s="48"/>
+      <c r="U53" s="48"/>
+    </row>
+    <row r="54" spans="1:21">
+      <c r="A54" s="39"/>
+      <c r="B54" s="39"/>
+      <c r="C54" s="39"/>
+      <c r="D54" s="39"/>
+      <c r="E54" s="39"/>
+      <c r="F54" s="39"/>
+      <c r="G54" s="39"/>
+      <c r="H54" s="39"/>
+      <c r="I54" s="39"/>
+      <c r="J54" s="39"/>
+      <c r="K54" s="39"/>
+      <c r="L54" s="39"/>
+      <c r="M54" s="39"/>
+      <c r="N54" s="39"/>
+      <c r="O54" s="39"/>
+      <c r="P54" s="39"/>
+      <c r="Q54" s="39"/>
+      <c r="R54" s="39"/>
+      <c r="S54" s="39"/>
+      <c r="T54" s="39"/>
+      <c r="U54" s="39"/>
+    </row>
     <row r="55" spans="1:21" ht="15.75">
-      <c r="A55" s="43" t="s">
+      <c r="A55" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="B55" s="43"/>
-      <c r="C55" s="43"/>
-      <c r="D55" s="43"/>
-      <c r="E55" s="43"/>
-      <c r="F55" s="43" t="s">
+      <c r="B55" s="49"/>
+      <c r="C55" s="49"/>
+      <c r="D55" s="49"/>
+      <c r="E55" s="49"/>
+      <c r="F55" s="49" t="s">
         <v>52</v>
       </c>
-      <c r="G55" s="43"/>
-      <c r="H55" s="44" t="s">
+      <c r="G55" s="49"/>
+      <c r="H55" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="I55" s="45"/>
-      <c r="J55" s="45"/>
-      <c r="K55" s="45"/>
-      <c r="L55" s="46"/>
-      <c r="M55" s="43" t="s">
+      <c r="I55" s="51"/>
+      <c r="J55" s="51"/>
+      <c r="K55" s="51"/>
+      <c r="L55" s="52"/>
+      <c r="M55" s="49" t="s">
         <v>54</v>
       </c>
-      <c r="N55" s="43"/>
-      <c r="O55" s="43"/>
-      <c r="P55" s="43"/>
-      <c r="Q55" s="43"/>
-      <c r="R55" s="43" t="s">
+      <c r="N55" s="49"/>
+      <c r="O55" s="49"/>
+      <c r="P55" s="49"/>
+      <c r="Q55" s="49"/>
+      <c r="R55" s="49" t="s">
         <v>55</v>
       </c>
-      <c r="S55" s="43"/>
-      <c r="T55" s="43"/>
-      <c r="U55" s="43"/>
+      <c r="S55" s="49"/>
+      <c r="T55" s="49"/>
+      <c r="U55" s="49"/>
     </row>
     <row r="56" spans="1:21">
-      <c r="A56" s="47">
+      <c r="A56" s="28">
         <v>45412</v>
       </c>
-      <c r="B56" s="47"/>
-      <c r="C56" s="48"/>
-      <c r="D56" s="48"/>
-      <c r="E56" s="48"/>
-      <c r="F56" s="49" t="s">
+      <c r="B56" s="28"/>
+      <c r="C56" s="29"/>
+      <c r="D56" s="29"/>
+      <c r="E56" s="29"/>
+      <c r="F56" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="G56" s="49"/>
-      <c r="H56" s="50" t="s">
+      <c r="G56" s="30"/>
+      <c r="H56" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="I56" s="51"/>
-      <c r="J56" s="51"/>
-      <c r="K56" s="51"/>
-      <c r="L56" s="52"/>
-      <c r="M56" s="48" t="s">
+      <c r="I56" s="32"/>
+      <c r="J56" s="32"/>
+      <c r="K56" s="32"/>
+      <c r="L56" s="33"/>
+      <c r="M56" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="N56" s="48"/>
-      <c r="O56" s="48"/>
-      <c r="P56" s="48"/>
-      <c r="Q56" s="48"/>
-      <c r="R56" s="48" t="s">
+      <c r="N56" s="29"/>
+      <c r="O56" s="29"/>
+      <c r="P56" s="29"/>
+      <c r="Q56" s="29"/>
+      <c r="R56" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="S56" s="48"/>
-      <c r="T56" s="48"/>
-      <c r="U56" s="48"/>
+      <c r="S56" s="29"/>
+      <c r="T56" s="29"/>
+      <c r="U56" s="29"/>
     </row>
     <row r="57" spans="1:21" ht="69.75" customHeight="1">
-      <c r="A57" s="47">
+      <c r="A57" s="28">
         <v>45777</v>
       </c>
-      <c r="B57" s="47"/>
-      <c r="C57" s="48"/>
-      <c r="D57" s="48"/>
-      <c r="E57" s="48"/>
-      <c r="F57" s="49" t="s">
+      <c r="B57" s="28"/>
+      <c r="C57" s="29"/>
+      <c r="D57" s="29"/>
+      <c r="E57" s="29"/>
+      <c r="F57" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="G57" s="49"/>
-      <c r="H57" s="50" t="s">
+      <c r="G57" s="30"/>
+      <c r="H57" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="I57" s="51"/>
-      <c r="J57" s="51"/>
-      <c r="K57" s="51"/>
-      <c r="L57" s="52"/>
-      <c r="M57" s="48" t="s">
+      <c r="I57" s="32"/>
+      <c r="J57" s="32"/>
+      <c r="K57" s="32"/>
+      <c r="L57" s="33"/>
+      <c r="M57" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="N57" s="48"/>
-      <c r="O57" s="48"/>
-      <c r="P57" s="48"/>
-      <c r="Q57" s="48"/>
-      <c r="R57" s="48" t="s">
+      <c r="N57" s="29"/>
+      <c r="O57" s="29"/>
+      <c r="P57" s="29"/>
+      <c r="Q57" s="29"/>
+      <c r="R57" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="S57" s="48"/>
-      <c r="T57" s="48"/>
-      <c r="U57" s="48"/>
+      <c r="S57" s="29"/>
+      <c r="T57" s="29"/>
+      <c r="U57" s="29"/>
     </row>
     <row r="58" spans="1:21" ht="35.25" customHeight="1">
-      <c r="A58" s="47">
+      <c r="A58" s="28">
         <v>46142</v>
       </c>
-      <c r="B58" s="48"/>
-      <c r="C58" s="48"/>
-      <c r="D58" s="48"/>
-      <c r="E58" s="48"/>
-      <c r="F58" s="53" t="s">
+      <c r="B58" s="29"/>
+      <c r="C58" s="29"/>
+      <c r="D58" s="29"/>
+      <c r="E58" s="29"/>
+      <c r="F58" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="G58" s="49"/>
-      <c r="H58" s="57" t="s">
+      <c r="G58" s="30"/>
+      <c r="H58" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="I58" s="58"/>
-      <c r="J58" s="58"/>
-      <c r="K58" s="58"/>
-      <c r="L58" s="59"/>
-      <c r="M58" s="48" t="s">
+      <c r="I58" s="36"/>
+      <c r="J58" s="36"/>
+      <c r="K58" s="36"/>
+      <c r="L58" s="37"/>
+      <c r="M58" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="N58" s="48"/>
-      <c r="O58" s="48"/>
-      <c r="P58" s="48"/>
-      <c r="Q58" s="48"/>
-      <c r="R58" s="48" t="s">
+      <c r="N58" s="29"/>
+      <c r="O58" s="29"/>
+      <c r="P58" s="29"/>
+      <c r="Q58" s="29"/>
+      <c r="R58" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="S58" s="48"/>
-      <c r="T58" s="48"/>
-      <c r="U58" s="48"/>
+      <c r="S58" s="29"/>
+      <c r="T58" s="29"/>
+      <c r="U58" s="29"/>
     </row>
   </sheetData>
-  <mergeCells count="53">
+  <mergeCells count="54">
+    <mergeCell ref="U1:U3"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="F7:G7"/>
     <mergeCell ref="A55:E55"/>
     <mergeCell ref="F55:G55"/>
     <mergeCell ref="H55:L55"/>
     <mergeCell ref="M55:Q55"/>
     <mergeCell ref="R55:U55"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="H56:L56"/>
+    <mergeCell ref="M56:Q56"/>
+    <mergeCell ref="R56:U56"/>
+    <mergeCell ref="A1:E6"/>
+    <mergeCell ref="B46:U46"/>
+    <mergeCell ref="B47:U47"/>
+    <mergeCell ref="B48:U48"/>
+    <mergeCell ref="B49:U49"/>
+    <mergeCell ref="T1:T3"/>
+    <mergeCell ref="B43:U43"/>
+    <mergeCell ref="B44:U44"/>
+    <mergeCell ref="B45:U45"/>
+    <mergeCell ref="F6:S6"/>
+    <mergeCell ref="I5:S5"/>
+    <mergeCell ref="F1:S1"/>
+    <mergeCell ref="F2:S3"/>
+    <mergeCell ref="I4:S4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="A52:U52"/>
+    <mergeCell ref="A54:U54"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="M7:P7"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="B50:U50"/>
+    <mergeCell ref="B51:U51"/>
+    <mergeCell ref="B53:U53"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="N8:S8"/>
     <mergeCell ref="A58:E58"/>
     <mergeCell ref="F58:G58"/>
     <mergeCell ref="H58:L58"/>
@@ -2961,44 +2995,6 @@
     <mergeCell ref="H57:L57"/>
     <mergeCell ref="M57:Q57"/>
     <mergeCell ref="R57:U57"/>
-    <mergeCell ref="A56:E56"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="H56:L56"/>
-    <mergeCell ref="M56:Q56"/>
-    <mergeCell ref="R56:U56"/>
-    <mergeCell ref="T1:T3"/>
-    <mergeCell ref="B53:U53"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="B8:G8"/>
-    <mergeCell ref="N8:S8"/>
-    <mergeCell ref="B48:U48"/>
-    <mergeCell ref="B49:U49"/>
-    <mergeCell ref="B50:U50"/>
-    <mergeCell ref="B51:U51"/>
-    <mergeCell ref="B52:U52"/>
-    <mergeCell ref="B43:U43"/>
-    <mergeCell ref="B44:U44"/>
-    <mergeCell ref="B45:U45"/>
-    <mergeCell ref="B46:U46"/>
-    <mergeCell ref="B47:U47"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U1:U3"/>
-    <mergeCell ref="T4:T5"/>
-    <mergeCell ref="U4:U5"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="M7:P7"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="A1:E6"/>
-    <mergeCell ref="F6:S6"/>
-    <mergeCell ref="I5:S5"/>
-    <mergeCell ref="F1:S1"/>
-    <mergeCell ref="F2:S3"/>
-    <mergeCell ref="I4:S4"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="F5:H5"/>
   </mergeCells>
   <pageMargins left="7.874015748031496E-2" right="7.874015748031496E-2" top="3.937007874015748E-2" bottom="3.937007874015748E-2" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="80" fitToHeight="0" orientation="landscape" r:id="rId1"/>
